--- a/HumanEval/TB Authors.xlsx
+++ b/HumanEval/TB Authors.xlsx
@@ -1,14 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LAB\ADR_DRAFT\DRAFT\HumanEval\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B694A6E-B1D2-4A44-A434-E16F28273533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="adyanshkakran@gmail.com" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="rudra.dhar@research.iiit.ac.in" sheetId="3" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="adyanshkakran@gmail.com" sheetId="2" r:id="rId2"/>
+    <sheet name="rudra.dhar@research.iiit.ac.in" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -159,24 +168,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -187,57 +198,45 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -427,28 +426,32 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:S65"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -507,121 +510,121 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>46237.90151462963</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="4">
-        <v>3849.0</v>
+      <c r="C2" s="3">
+        <v>3849</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I2" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N2" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q2" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R2" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>46237.902834305554</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="4">
-        <v>1353.0</v>
+      <c r="C3" s="3">
+        <v>1353</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46237.90372259259</v>
+        <v>46237.903722592593</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="4">
-        <v>3382.0</v>
+      <c r="C4" s="3">
+        <v>3382</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>26</v>
@@ -630,66 +633,66 @@
         <v>22</v>
       </c>
       <c r="I4" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M4" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N4" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q4" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R4" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46237.90481083334</v>
+        <v>46237.904810833337</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4">
-        <v>4223.0</v>
+      <c r="C5" s="3">
+        <v>4223</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J5" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M5" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>28</v>
@@ -698,753 +701,753 @@
         <v>23</v>
       </c>
       <c r="Q5" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46237.90543737268</v>
+        <v>46237.905437372683</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4">
-        <v>3846.0</v>
+      <c r="C6" s="3">
+        <v>3846</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M6" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q6" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R6" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46237.906167928246</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4">
-        <v>51.0</v>
+      <c r="C7" s="3">
+        <v>51</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I7" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M7" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N7" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q7" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46237.907328009256</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="4">
-        <v>1684.0</v>
+      <c r="C8" s="3">
+        <v>1684</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J8" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M8" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N8" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q8" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R8" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46237.90853486111</v>
+        <v>46237.908534861112</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="4">
-        <v>2896.0</v>
+      <c r="C9" s="3">
+        <v>2896</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E9" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J9" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M9" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N9" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q9" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R9" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46237.9096111574</v>
+        <v>46237.909611157404</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="4">
-        <v>250.0</v>
+      <c r="C10" s="3">
+        <v>250</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M10" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N10" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q10" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R10" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46237.91034965278</v>
+        <v>46237.910349652782</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="4">
-        <v>2875.0</v>
+      <c r="C11" s="3">
+        <v>2875</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M11" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N11" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q11" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R11" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46237.9110550926</v>
+        <v>46237.911055092598</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="4">
-        <v>3325.0</v>
+      <c r="C12" s="3">
+        <v>3325</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M12" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N12" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q12" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R12" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>46237.925493229166</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="4">
-        <v>1610.0</v>
+      <c r="C13" s="3">
+        <v>1610</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F13" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M13" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N13" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q13" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R13" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46237.92597502314</v>
+        <v>46237.925975023143</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="4">
-        <v>844.0</v>
+      <c r="C14" s="3">
+        <v>844</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F14" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I14" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M14" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N14" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q14" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R14" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46237.93662741898</v>
+        <v>46237.936627418982</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="4">
-        <v>3013.0</v>
+      <c r="C15" s="3">
+        <v>3013</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I15" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M15" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q15" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46237.93730505787</v>
+        <v>46237.937305057872</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="4">
-        <v>3159.0</v>
+      <c r="C16" s="3">
+        <v>3159</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F16" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J16" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M16" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N16" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q16" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R16" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>46237.93907375</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="4">
-        <v>740.0</v>
+      <c r="C17" s="3">
+        <v>740</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F17" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J17" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M17" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N17" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q17" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R17" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46237.94033936343</v>
+        <v>46237.940339363427</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="4">
-        <v>3596.0</v>
+      <c r="C18" s="3">
+        <v>3596</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F18" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I18" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J18" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M18" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N18" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q18" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="R18" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>46237.941739629634</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="4">
-        <v>2804.0</v>
+      <c r="C19" s="3">
+        <v>2804</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E19" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F19" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I19" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J19" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M19" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N19" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q19" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R19" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46237.94263384259</v>
+        <v>46237.942633842591</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="4">
-        <v>3231.0</v>
+      <c r="C20" s="3">
+        <v>3231</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E20" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M20" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N20" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q20" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R20" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46237.94383600695</v>
+        <v>46237.943836006947</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="4">
-        <v>121.0</v>
+      <c r="C21" s="3">
+        <v>121</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E21" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F21" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I21" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M21" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>34</v>
@@ -1453,86 +1456,86 @@
         <v>23</v>
       </c>
       <c r="Q21" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R21" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46237.94586731482</v>
+        <v>46237.945867314818</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="4">
-        <v>3247.0</v>
+      <c r="C22" s="3">
+        <v>3247</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M22" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N22" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q22" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R22" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46237.94781737268</v>
+        <v>46237.947817372682</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="4">
-        <v>3926.0</v>
+      <c r="C23" s="3">
+        <v>3926</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I23" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>34</v>
@@ -1541,415 +1544,415 @@
         <v>23</v>
       </c>
       <c r="M23" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N23" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q23" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R23" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46237.95429418981</v>
+        <v>46237.954294189811</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="4">
-        <v>1069.0</v>
+      <c r="C24" s="3">
+        <v>1069</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F24" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I24" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J24" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M24" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N24" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q24" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>46237.95576960648</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="4">
-        <v>560.0</v>
+      <c r="C25" s="3">
+        <v>560</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E25" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F25" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I25" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M25" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N25" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q25" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R25" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46237.95758190972</v>
+        <v>46237.957581909723</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="4">
-        <v>3056.0</v>
+      <c r="C26" s="3">
+        <v>3056</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E26" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F26" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I26" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J26" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M26" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N26" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q26" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R26" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46237.95899717593</v>
+        <v>46237.958997175927</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="4">
-        <v>3341.0</v>
+      <c r="C27" s="3">
+        <v>3341</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E27" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F27" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I27" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J27" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M27" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N27" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q27" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46237.96013150463</v>
+        <v>46237.960131504631</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="4">
-        <v>3508.0</v>
+      <c r="C28" s="3">
+        <v>3508</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E28" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F28" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I28" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M28" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N28" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q28" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R28" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46237.96396145833</v>
+        <v>46237.963961458328</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="4">
-        <v>1952.0</v>
+      <c r="C29" s="3">
+        <v>1952</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E29" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F29" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I29" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J29" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N29" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q29" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R29" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46237.96491210649</v>
+        <v>46237.964912106487</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="4">
-        <v>429.0</v>
+      <c r="C30" s="3">
+        <v>429</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E30" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F30" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J30" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M30" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N30" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q30" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R30" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46237.96651601852</v>
+        <v>46237.966516018518</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="4">
-        <v>501.0</v>
+      <c r="C31" s="3">
+        <v>501</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F31" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I31" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J31" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M31" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N31" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P31" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q31" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R31" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46237.96746697917</v>
+        <v>46237.967466979171</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="4">
-        <v>1275.0</v>
+      <c r="C32" s="3">
+        <v>1275</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E32" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>38</v>
@@ -1958,1597 +1961,1598 @@
         <v>23</v>
       </c>
       <c r="I32" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J32" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M32" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N32" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q32" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R32" s="3">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46237.96944447917</v>
+        <v>46237.969444479168</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="4">
-        <v>4168.0</v>
+      <c r="C33" s="3">
+        <v>4168</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E33" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F33" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I33" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M33" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N33" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q33" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R33" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46237.97014508102</v>
+        <v>46237.970145081017</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="4">
-        <v>1482.0</v>
+      <c r="C34" s="3">
+        <v>1482</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E34" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I34" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J34" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M34" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q34" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>46237.99224663194</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="4">
-        <v>1876.0</v>
+      <c r="C35" s="3">
+        <v>1876</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E35" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F35" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I35" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J35" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M35" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N35" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q35" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R35" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46237.99273665509</v>
+        <v>46237.992736655091</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C36" s="4">
-        <v>1213.0</v>
+      <c r="C36" s="3">
+        <v>1213</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E36" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F36" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I36" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J36" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M36" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N36" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q36" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R36" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>46237.99337837963</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="4">
-        <v>2016.0</v>
+      <c r="C37" s="3">
+        <v>2016</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E37" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F37" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I37" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J37" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M37" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N37" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q37" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R37" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46237.99400883102</v>
+        <v>46237.994008831018</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="4">
-        <v>3379.0</v>
+      <c r="C38" s="3">
+        <v>3379</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E38" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I38" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M38" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N38" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q38" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="R38" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>46237.994517037034</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="4">
-        <v>3397.0</v>
+      <c r="C39" s="3">
+        <v>3397</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E39" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F39" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I39" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J39" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M39" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N39" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q39" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R39" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46237.99496386574</v>
+        <v>46237.994963865742</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="4">
-        <v>1985.0</v>
+      <c r="C40" s="3">
+        <v>1985</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F40" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I40" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J40" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M40" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N40" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P40" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q40" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R40" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>46237.99550827546</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="4">
-        <v>949.0</v>
+      <c r="C41" s="3">
+        <v>949</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E41" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F41" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I41" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J41" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M41" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N41" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q41" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="R41" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>46237.996130810185</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="4">
-        <v>3284.0</v>
+      <c r="C42" s="3">
+        <v>3284</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F42" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I42" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J42" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M42" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N42" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q42" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R42" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>46237.997184074076</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="4">
-        <v>2889.0</v>
+      <c r="C43" s="3">
+        <v>2889</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E43" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F43" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I43" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J43" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M43" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N43" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q43" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="R43" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46237.99814098379</v>
+        <v>46237.998140983793</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="4">
-        <v>709.0</v>
+      <c r="C44" s="3">
+        <v>709</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E44" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I44" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J44" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M44" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N44" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q44" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R44" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>46237.998667175925</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="4">
-        <v>3096.0</v>
+      <c r="C45" s="3">
+        <v>3096</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E45" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F45" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I45" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J45" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M45" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N45" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q45" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R45" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46237.99936909722</v>
+        <v>46237.999369097219</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="4">
-        <v>982.0</v>
+      <c r="C46" s="3">
+        <v>982</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E46" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F46" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I46" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J46" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M46" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N46" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q46" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R46" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>46238.000505289354</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="4">
-        <v>3344.0</v>
+      <c r="C47" s="3">
+        <v>3344</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E47" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F47" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I47" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J47" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M47" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N47" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q47" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R47" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>46238.001392314814</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C48" s="4">
-        <v>1375.0</v>
+      <c r="C48" s="3">
+        <v>1375</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E48" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F48" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I48" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M48" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N48" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q48" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R48" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46238.00233445602</v>
+        <v>46238.002334456018</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="4">
-        <v>993.0</v>
+      <c r="C49" s="3">
+        <v>993</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E49" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F49" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I49" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J49" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M49" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N49" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q49" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R49" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>46238.00276456018</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C50" s="4">
-        <v>3812.0</v>
+      <c r="C50" s="3">
+        <v>3812</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E50" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F50" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I50" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J50" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M50" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N50" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q50" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R50" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>46238.003434583334</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="4">
-        <v>1614.0</v>
+      <c r="C51" s="3">
+        <v>1614</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E51" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F51" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I51" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M51" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N51" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q51" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R51" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46238.00404322917</v>
+        <v>46238.004043229172</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="4">
-        <v>855.0</v>
+      <c r="C52" s="3">
+        <v>855</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E52" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F52" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I52" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J52" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M52" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N52" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q52" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R52" s="3">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>46238.004888449075</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C53" s="4">
-        <v>4234.0</v>
+      <c r="C53" s="3">
+        <v>4234</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E53" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F53" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I53" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J53" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M53" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N53" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q53" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R53" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46238.00717652778</v>
+        <v>46238.007176527783</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="4">
-        <v>3286.0</v>
+      <c r="C54" s="3">
+        <v>3286</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E54" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F54" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I54" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J54" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M54" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N54" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q54" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R54" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46238.00823315972</v>
+        <v>46238.008233159722</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="4">
-        <v>3652.0</v>
+      <c r="C55" s="3">
+        <v>3652</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E55" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F55" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I55" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J55" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M55" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N55" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q55" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R55" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>46238.013038819445</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="4">
-        <v>3824.0</v>
+      <c r="C56" s="3">
+        <v>3824</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E56" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F56" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I56" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J56" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M56" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N56" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q56" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="R56" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>46238.013499548615</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="4">
-        <v>2911.0</v>
+      <c r="C57" s="3">
+        <v>2911</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E57" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F57" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I57" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J57" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M57" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N57" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q57" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R57" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>46238.013881122686</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="4">
-        <v>2062.0</v>
+      <c r="C58" s="3">
+        <v>2062</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E58" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F58" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I58" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J58" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M58" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N58" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q58" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R58" s="3">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46238.01580121528</v>
+        <v>46238.015801215282</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C59" s="4">
-        <v>3143.0</v>
+      <c r="C59" s="3">
+        <v>3143</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E59" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I59" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J59" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M59" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N59" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q59" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R59" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46238.02113542824</v>
+        <v>46238.021135428236</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="4">
-        <v>4075.0</v>
+      <c r="C60" s="3">
+        <v>4075</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E60" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F60" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I60" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J60" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M60" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N60" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q60" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R60" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46238.02242260417</v>
+        <v>46238.022422604168</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="4">
-        <v>4075.0</v>
+      <c r="C61" s="3">
+        <v>66</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E61" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F61" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I61" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J61" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M61" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N61" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q61" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R61" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46238.02304233796</v>
+        <v>46238.023042337962</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C62" s="4">
-        <v>66.0</v>
+      <c r="C62" s="3">
+        <v>2544</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E62" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F62" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I62" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J62" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M62" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N62" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q62" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R62" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>46238.02366741898</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C63" s="4">
-        <v>2544.0</v>
+      <c r="C63" s="3">
+        <v>3881</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E63" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F63" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I63" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M63" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N63" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q63" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R63" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46238.02491504629</v>
+        <v>46238.024915046291</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C64" s="4">
-        <v>3881.0</v>
+      <c r="C64" s="3">
+        <v>986</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E64" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F64" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I64" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J64" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M64" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N64" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q64" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R64" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46238.02591829861</v>
+        <v>46238.025918298612</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C65" s="4">
-        <v>986.0</v>
+      <c r="C65" s="3">
+        <v>945</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E65" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F65" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I65" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J65" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M65" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N65" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P65" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q65" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R65" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:S65"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3607,71 +3611,71 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>46222.172217025465</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="4">
-        <v>3849.0</v>
+      <c r="C2" s="3">
+        <v>3849</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M2" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N2" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q2" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R2" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>46225.60102349537</v>
+        <v>46225.601023495372</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="4">
-        <v>1353.0</v>
+      <c r="C3" s="3">
+        <v>1353</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>27</v>
@@ -3680,10 +3684,10 @@
         <v>20</v>
       </c>
       <c r="I3" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>27</v>
@@ -3692,10 +3696,10 @@
         <v>23</v>
       </c>
       <c r="M3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>27</v>
@@ -3704,42 +3708,42 @@
         <v>21</v>
       </c>
       <c r="Q3" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46225.624809444445</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="4">
-        <v>3382.0</v>
+      <c r="C4" s="3">
+        <v>3382</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>29</v>
@@ -3748,48 +3752,48 @@
         <v>21</v>
       </c>
       <c r="M4" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N4" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q4" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R4" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46225.62852349537</v>
+        <v>46225.628523495368</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="4">
-        <v>4223.0</v>
+      <c r="C5" s="3">
+        <v>4223</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>30</v>
@@ -3798,10 +3802,10 @@
         <v>21</v>
       </c>
       <c r="M5" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>31</v>
@@ -3810,424 +3814,424 @@
         <v>22</v>
       </c>
       <c r="Q5" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R5" s="3">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46230.09894773148</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="4">
-        <v>3846.0</v>
+      <c r="C6" s="3">
+        <v>3846</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F6" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M6" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N6" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q6" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R6" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46230.10650782408</v>
+        <v>46230.106507824079</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="4">
-        <v>51.0</v>
+      <c r="C7" s="3">
+        <v>51</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I7" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M7" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N7" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q7" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46230.113922743054</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="4">
-        <v>1684.0</v>
+      <c r="C8" s="3">
+        <v>1684</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F8" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M8" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N8" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q8" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R8" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>46230.123343009254</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="4">
-        <v>2896.0</v>
+      <c r="C9" s="3">
+        <v>2896</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M9" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N9" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q9" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R9" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46231.84139128472</v>
+        <v>46231.841391284717</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="4">
-        <v>250.0</v>
+      <c r="C10" s="3">
+        <v>250</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I10" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M10" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N10" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q10" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R10" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46231.84536614583</v>
+        <v>46231.845366145833</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="4">
-        <v>2875.0</v>
+      <c r="C11" s="3">
+        <v>2875</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J11" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M11" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N11" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q11" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R11" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46232.75054260417</v>
+        <v>46232.750542604168</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="4">
-        <v>3325.0</v>
+      <c r="C12" s="3">
+        <v>3325</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M12" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N12" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q12" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46232.75557686343</v>
+        <v>46232.755576863427</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="4">
-        <v>1610.0</v>
+      <c r="C13" s="3">
+        <v>1610</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M13" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N13" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q13" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R13" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>46232.76180821759</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="4">
-        <v>844.0</v>
+      <c r="C14" s="3">
+        <v>844</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F14" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M14" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N14" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>32</v>
@@ -4236,77 +4240,77 @@
         <v>20</v>
       </c>
       <c r="Q14" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R14" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46232.76564729167</v>
+        <v>46232.765647291671</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="4">
-        <v>3013.0</v>
+      <c r="C15" s="3">
+        <v>3013</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E15" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M15" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q15" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>46232.776407812504</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="4">
-        <v>3159.0</v>
+      <c r="C16" s="3">
+        <v>3159</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>33</v>
@@ -4315,207 +4319,207 @@
         <v>22</v>
       </c>
       <c r="I16" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M16" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q16" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46232.78047136574</v>
+        <v>46232.780471365739</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="4">
-        <v>740.0</v>
+      <c r="C17" s="3">
+        <v>740</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M17" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q17" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46232.78326053241</v>
+        <v>46232.783260532407</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="4">
-        <v>3596.0</v>
+      <c r="C18" s="3">
+        <v>3596</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F18" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I18" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M18" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q18" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R18" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46232.78644847222</v>
+        <v>46232.786448472223</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="4">
-        <v>2804.0</v>
+      <c r="C19" s="3">
+        <v>2804</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E19" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F19" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J19" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M19" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N19" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q19" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R19" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46232.78936142361</v>
+        <v>46232.789361423609</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="4">
-        <v>3231.0</v>
+      <c r="C20" s="3">
+        <v>3231</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E20" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I20" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M20" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>35</v>
@@ -4524,39 +4528,39 @@
         <v>23</v>
       </c>
       <c r="Q20" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46232.79335375</v>
+        <v>46232.793353749999</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="4">
-        <v>121.0</v>
+      <c r="C21" s="3">
+        <v>121</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E21" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I21" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>36</v>
@@ -4565,10 +4569,10 @@
         <v>20</v>
       </c>
       <c r="M21" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>37</v>
@@ -4577,518 +4581,518 @@
         <v>23</v>
       </c>
       <c r="Q21" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46232.85918023148</v>
+        <v>46232.859180231477</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="4">
-        <v>3247.0</v>
+      <c r="C22" s="3">
+        <v>3247</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E22" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I22" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M22" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q22" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46232.86953215278</v>
+        <v>46232.869532152778</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="4">
-        <v>3926.0</v>
+      <c r="C23" s="3">
+        <v>3926</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E23" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I23" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M23" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N23" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q23" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R23" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46232.87688391204</v>
+        <v>46232.876883912038</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="4">
-        <v>1069.0</v>
+      <c r="C24" s="3">
+        <v>1069</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I24" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M24" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q24" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46232.88261299768</v>
+        <v>46232.882612997681</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="4">
-        <v>560.0</v>
+      <c r="C25" s="3">
+        <v>560</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E25" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F25" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I25" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M25" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N25" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q25" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R25" s="3">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46233.00159622685</v>
+        <v>46233.001596226852</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="4">
-        <v>3056.0</v>
+      <c r="C26" s="3">
+        <v>3056</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E26" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I26" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M26" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N26" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q26" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R26" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46233.01361976852</v>
+        <v>46233.013619768521</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="4">
-        <v>3341.0</v>
+      <c r="C27" s="3">
+        <v>3341</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I27" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M27" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q27" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>46234.068551226854</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="4">
-        <v>3508.0</v>
+      <c r="C28" s="3">
+        <v>3508</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F28" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I28" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M28" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q28" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>46234.070875694444</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="4">
-        <v>1952.0</v>
+      <c r="C29" s="3">
+        <v>1952</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F29" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I29" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J29" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M29" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N29" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q29" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R29" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46234.07546523148</v>
+        <v>46234.075465231479</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="4">
-        <v>429.0</v>
+      <c r="C30" s="3">
+        <v>429</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F30" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I30" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J30" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M30" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N30" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q30" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R30" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>46234.087179236114</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="4">
-        <v>501.0</v>
+      <c r="C31" s="3">
+        <v>501</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F31" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I31" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J31" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M31" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N31" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P31" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q31" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R31" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46234.0930824074</v>
+        <v>46234.093082407402</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="4">
-        <v>1275.0</v>
+      <c r="C32" s="3">
+        <v>1275</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F32" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I32" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M32" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>39</v>
@@ -5097,30 +5101,30 @@
         <v>20</v>
       </c>
       <c r="Q32" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R32" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>46234.103163645836</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="4">
-        <v>4168.0</v>
+      <c r="C33" s="3">
+        <v>4168</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E33" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F33" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>40</v>
@@ -5129,48 +5133,48 @@
         <v>22</v>
       </c>
       <c r="I33" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J33" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M33" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N33" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q33" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R33" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46238.82448619213</v>
+        <v>46238.824486192127</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="4">
-        <v>1482.0</v>
+      <c r="C34" s="3">
+        <v>1482</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E34" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>41</v>
@@ -5179,10 +5183,10 @@
         <v>21</v>
       </c>
       <c r="I34" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>41</v>
@@ -5191,10 +5195,10 @@
         <v>20</v>
       </c>
       <c r="M34" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N34" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>41</v>
@@ -5203,51 +5207,51 @@
         <v>22</v>
       </c>
       <c r="Q34" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>46238.83467055556</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="4">
-        <v>1876.0</v>
+      <c r="C35" s="3">
+        <v>1876</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E35" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F35" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I35" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J35" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M35" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N35" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>42</v>
@@ -5256,39 +5260,39 @@
         <v>23</v>
       </c>
       <c r="Q35" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R35" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46238.84257037037</v>
+        <v>46238.842570370369</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="4">
-        <v>1213.0</v>
+      <c r="C36" s="3">
+        <v>1213</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E36" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I36" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>43</v>
@@ -5297,48 +5301,48 @@
         <v>22</v>
       </c>
       <c r="M36" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q36" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46238.84952280093</v>
+        <v>46238.849522800927</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="4">
-        <v>2016.0</v>
+      <c r="C37" s="3">
+        <v>2016</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E37" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F37" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I37" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>43</v>
@@ -5347,104 +5351,104 @@
         <v>22</v>
       </c>
       <c r="M37" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N37" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q37" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R37" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46244.98406592592</v>
+        <v>46244.984065925921</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="4">
-        <v>3379.0</v>
+      <c r="C38" s="3">
+        <v>3379</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E38" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I38" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J38" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M38" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N38" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q38" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="R38" s="3">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>46244.991957743056</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="4">
-        <v>3397.0</v>
+      <c r="C39" s="3">
+        <v>3397</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E39" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F39" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I39" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J39" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M39" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N39" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O39" s="3" t="s">
         <v>40</v>
@@ -5453,86 +5457,86 @@
         <v>22</v>
       </c>
       <c r="Q39" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R39" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>46244.999857013885</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="4">
-        <v>1985.0</v>
+      <c r="C40" s="3">
+        <v>1985</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E40" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F40" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I40" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J40" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M40" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N40" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q40" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R40" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>46245.00216123843</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="4">
-        <v>949.0</v>
+      <c r="C41" s="3">
+        <v>949</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E41" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F41" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I41" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J41" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>40</v>
@@ -5541,283 +5545,283 @@
         <v>22</v>
       </c>
       <c r="M41" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N41" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q41" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R41" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46245.06479855324</v>
+        <v>46245.064798553241</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="4">
-        <v>3284.0</v>
+      <c r="C42" s="3">
+        <v>3284</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E42" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F42" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I42" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J42" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M42" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N42" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q42" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R42" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46245.06901409722</v>
+        <v>46245.069014097222</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="4">
-        <v>2889.0</v>
+      <c r="C43" s="3">
+        <v>2889</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E43" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F43" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I43" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J43" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M43" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N43" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q43" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R43" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>46245.071389386576</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="4">
-        <v>709.0</v>
+      <c r="C44" s="3">
+        <v>709</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E44" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I44" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M44" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N44" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q44" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R44" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>46245.076771990745</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="4">
-        <v>3096.0</v>
+      <c r="C45" s="3">
+        <v>3096</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E45" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F45" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I45" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J45" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M45" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N45" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q45" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R45" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>46245.08922303241</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C46" s="4">
-        <v>982.0</v>
+      <c r="C46" s="3">
+        <v>982</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E46" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F46" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I46" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J46" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M46" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N46" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q46" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R46" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>46245.094949074075</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C47" s="4">
-        <v>3344.0</v>
+      <c r="C47" s="3">
+        <v>3344</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E47" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F47" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I47" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J47" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>45</v>
@@ -5826,189 +5830,189 @@
         <v>20</v>
       </c>
       <c r="M47" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N47" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q47" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R47" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46245.09878515046</v>
+        <v>46245.098785150461</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="4">
-        <v>1375.0</v>
+      <c r="C48" s="3">
+        <v>1375</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E48" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F48" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I48" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J48" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M48" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N48" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q48" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R48" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46245.10444263888</v>
+        <v>46245.104442638883</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="4">
-        <v>993.0</v>
+      <c r="C49" s="3">
+        <v>993</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E49" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F49" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I49" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J49" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M49" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N49" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q49" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R49" s="3">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46246.09928751158</v>
+        <v>46246.099287511577</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="4">
-        <v>3812.0</v>
+      <c r="C50" s="3">
+        <v>3812</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E50" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F50" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I50" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J50" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M50" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N50" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q50" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R50" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46246.10415792824</v>
+        <v>46246.104157928239</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C51" s="4">
-        <v>1614.0</v>
+      <c r="C51" s="3">
+        <v>1614</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E51" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F51" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I51" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J51" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>33</v>
@@ -6017,603 +6021,603 @@
         <v>23</v>
       </c>
       <c r="M51" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N51" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q51" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R51" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46246.10643712963</v>
+        <v>46246.106437129631</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="4">
-        <v>855.0</v>
+      <c r="C52" s="3">
+        <v>855</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E52" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I52" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J52" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M52" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N52" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q52" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R52" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>46246.110177083334</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C53" s="4">
-        <v>4234.0</v>
+      <c r="C53" s="3">
+        <v>4234</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E53" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I53" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M53" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N53" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q53" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R53" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46246.68995649306</v>
+        <v>46246.689956493057</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="4">
-        <v>3286.0</v>
+      <c r="C54" s="3">
+        <v>3286</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E54" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I54" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J54" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M54" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N54" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q54" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R54" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46246.69855392361</v>
+        <v>46246.698553923612</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="4">
-        <v>3652.0</v>
+      <c r="C55" s="3">
+        <v>3652</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E55" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I55" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M55" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N55" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="Q55" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46246.70038637731</v>
+        <v>46246.700386377313</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="4">
-        <v>3824.0</v>
+      <c r="C56" s="3">
+        <v>3824</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E56" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F56" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I56" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J56" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M56" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N56" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q56" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R56" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46246.70582190972</v>
+        <v>46246.705821909723</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="4">
-        <v>2911.0</v>
+      <c r="C57" s="3">
+        <v>2911</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E57" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F57" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I57" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J57" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M57" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N57" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q57" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R57" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>46247.10651681713</v>
+        <v>46247.106516817134</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="4">
-        <v>2062.0</v>
+      <c r="C58" s="3">
+        <v>2062</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E58" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F58" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I58" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J58" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M58" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N58" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q58" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="R58" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46247.11941072917</v>
+        <v>46247.119410729167</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C59" s="4">
-        <v>3143.0</v>
+      <c r="C59" s="3">
+        <v>3143</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E59" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I59" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M59" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N59" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q59" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R59" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46247.12811152778</v>
+        <v>46247.128111527782</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="4">
-        <v>4075.0</v>
+      <c r="C60" s="3">
+        <v>4075</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E60" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F60" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I60" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J60" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M60" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N60" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>20</v>
       </c>
       <c r="Q60" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R60" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46247.13212930555</v>
+        <v>46247.132129305552</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C61" s="4">
-        <v>66.0</v>
+      <c r="C61" s="3">
+        <v>66</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E61" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F61" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I61" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J61" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>20</v>
       </c>
       <c r="M61" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N61" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q61" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R61" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46247.67846491898</v>
+        <v>46247.678464918979</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C62" s="4">
-        <v>2544.0</v>
+      <c r="C62" s="3">
+        <v>2544</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E62" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I62" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M62" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N62" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q62" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>46247.747536180555</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C63" s="4">
-        <v>3881.0</v>
+      <c r="C63" s="3">
+        <v>3881</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E63" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F63" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I63" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M63" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N63" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="Q63" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="R63" s="3">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>46247.751237627315</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C64" s="4">
-        <v>986.0</v>
+      <c r="C64" s="3">
+        <v>986</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E64" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>46</v>
@@ -6622,10 +6626,10 @@
         <v>23</v>
       </c>
       <c r="I64" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>46</v>
@@ -6634,10 +6638,10 @@
         <v>22</v>
       </c>
       <c r="M64" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N64" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O64" s="3" t="s">
         <v>46</v>
@@ -6646,63 +6650,63 @@
         <v>21</v>
       </c>
       <c r="Q64" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="S64" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46247.75870796296</v>
+        <v>46247.758707962959</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C65" s="4">
-        <v>945.0</v>
+      <c r="C65" s="3">
+        <v>945</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E65" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F65" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I65" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J65" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M65" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N65" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="Q65" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="R65" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>